--- a/selenium-web-tests/selenium_report.xlsx
+++ b/selenium-web-tests/selenium_report.xlsx
@@ -20,7 +20,7 @@
     <t>Run Date</t>
   </si>
   <si>
-    <t>18/6/2026, 2:59:12 pm</t>
+    <t>19/6/2026, 8:46:40 am</t>
   </si>
   <si>
     <t>Total Test Cases</t>
